--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1526-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1526-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E22F69D9-0696-4DA6-AEBE-751ECE7AA52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6DA53FD-CA14-44DF-B51D-D2812EF72FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{718427A6-F0B8-4DFD-97CC-A5FE004883DD}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D80E8C33-9D1A-41AD-8C46-7CC58183E476}"/>
   </bookViews>
   <sheets>
     <sheet name="1526-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1478,25 +1478,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2ADB46D-7FF1-487A-97D5-8681FAB7A404}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FE99C15-3349-4CC9-974A-8CE40B8DC3BD}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1566,7 +1566,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1686,7 +1686,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>9.9600000000000009</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2418,7 +2418,7 @@
         <v>5.46</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>6.49</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2020</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2019</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2018</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>4.3099999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2017</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2016</v>
       </c>
@@ -2924,7 +2924,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2015</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>3.42</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2014</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2013</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2012</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2011</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2010</v>
       </c>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2009</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2008</v>
       </c>
@@ -3500,7 +3500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2007</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2006</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2005</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2004</v>
       </c>
@@ -3788,7 +3788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2003</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2002</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2001</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2000</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>1999</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1998</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1997</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1996</v>
       </c>
@@ -4364,7 +4364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
         <v>47</v>
       </c>
